--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>31.77131973457852</v>
+      </c>
+      <c r="C2">
         <v>19.32907348242811</v>
-      </c>
-      <c r="C2">
-        <v>31.77131973457852</v>
       </c>
       <c r="D2">
         <v>5.173553719008265</v>
       </c>
       <c r="E2">
-        <v>12.79220594394363</v>
+        <v>21.0266294204472</v>
       </c>
       <c r="F2">
         <v>66.18116463560918</v>
       </c>
       <c r="G2">
-        <v>21.0266294204472</v>
+        <v>12.79220594394363</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.10929909784872</v>
+      </c>
+      <c r="C3">
         <v>28.07078417765441</v>
-      </c>
-      <c r="C3">
-        <v>30.10929909784872</v>
       </c>
       <c r="D3">
         <v>3.562422744128554</v>
       </c>
       <c r="E3">
-        <v>17.74609267891417</v>
+        <v>19.03482314230875</v>
       </c>
       <c r="F3">
         <v>63.21908417877707</v>
       </c>
       <c r="G3">
-        <v>19.03482314230875</v>
+        <v>17.74609267891417</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.04656319290466</v>
+      </c>
+      <c r="C4">
         <v>40.26607538802661</v>
-      </c>
-      <c r="C4">
-        <v>29.04656319290466</v>
       </c>
       <c r="D4">
         <v>2.483480176211454</v>
       </c>
       <c r="E4">
-        <v>23.78208486118386</v>
+        <v>17.15557883708748</v>
       </c>
       <c r="F4">
         <v>59.06233630172866</v>
       </c>
       <c r="G4">
-        <v>17.15557883708748</v>
+        <v>23.78208486118386</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.16121555498326</v>
+      </c>
+      <c r="C5">
         <v>34.27762039660057</v>
-      </c>
-      <c r="C5">
-        <v>28.16121555498326</v>
       </c>
       <c r="D5">
         <v>2.917355371900826</v>
       </c>
       <c r="E5">
+        <v>17.33650416171225</v>
+      </c>
+      <c r="F5">
+        <v>61.56163297661514</v>
+      </c>
+      <c r="G5">
         <v>21.10186286167261</v>
-      </c>
-      <c r="F5">
-        <v>61.56163297661513</v>
-      </c>
-      <c r="G5">
-        <v>17.33650416171225</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.05134474327628</v>
+      </c>
+      <c r="C6">
         <v>25.97207981702027</v>
-      </c>
-      <c r="C6">
-        <v>31.05134474327628</v>
       </c>
       <c r="D6">
         <v>3.850288490737929</v>
       </c>
       <c r="E6">
-        <v>16.54025817469486</v>
+        <v>19.77497614144357</v>
       </c>
       <c r="F6">
         <v>63.68476568386157</v>
       </c>
       <c r="G6">
-        <v>19.77497614144357</v>
+        <v>16.54025817469486</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.80198923259422</v>
+      </c>
+      <c r="C7">
         <v>33.50670681631536</v>
-      </c>
-      <c r="C7">
-        <v>29.80198923259422</v>
       </c>
       <c r="D7">
         <v>2.984477124183007</v>
       </c>
       <c r="E7">
-        <v>20.5174051517014</v>
+        <v>18.24886852545119</v>
       </c>
       <c r="F7">
         <v>61.2337263228474</v>
       </c>
       <c r="G7">
-        <v>18.24886852545119</v>
+        <v>20.5174051517014</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.42234772085518</v>
+      </c>
+      <c r="C8">
         <v>25.99435256151674</v>
-      </c>
-      <c r="C8">
-        <v>27.42234772085518</v>
       </c>
       <c r="D8">
         <v>3.846989447548107</v>
       </c>
       <c r="E8">
-        <v>16.94362641985697</v>
+        <v>17.874421539756</v>
       </c>
       <c r="F8">
         <v>65.18195204038705</v>
       </c>
       <c r="G8">
-        <v>17.874421539756</v>
+        <v>16.94362641985697</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>26.22780604298619</v>
+      </c>
+      <c r="C9">
         <v>35.53109749766379</v>
-      </c>
-      <c r="C9">
-        <v>26.22780604298619</v>
       </c>
       <c r="D9">
         <v>2.814436002337814</v>
       </c>
       <c r="E9">
-        <v>21.96546633288401</v>
+        <v>16.21413441170807</v>
       </c>
       <c r="F9">
         <v>61.82039925540792</v>
       </c>
       <c r="G9">
-        <v>16.21413441170807</v>
+        <v>21.96546633288401</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.01166372581272</v>
+      </c>
+      <c r="C10">
         <v>21.27284146304991</v>
-      </c>
-      <c r="C10">
-        <v>30.01166372581272</v>
       </c>
       <c r="D10">
         <v>4.700829467172782</v>
       </c>
       <c r="E10">
-        <v>14.06148067608975</v>
+        <v>19.8378966096669</v>
       </c>
       <c r="F10">
         <v>66.10062271424336</v>
       </c>
       <c r="G10">
-        <v>19.8378966096669</v>
+        <v>14.06148067608975</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>28.00204241004385</v>
+      </c>
+      <c r="C11">
         <v>21.95590797140626</v>
-      </c>
-      <c r="C11">
-        <v>28.00204241004385</v>
       </c>
       <c r="D11">
         <v>4.554582763337893</v>
       </c>
       <c r="E11">
-        <v>14.64137640955796</v>
+        <v>18.67326296392733</v>
       </c>
       <c r="F11">
         <v>66.68536062651471</v>
       </c>
       <c r="G11">
-        <v>18.67326296392734</v>
+        <v>14.64137640955795</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.11852743849991</v>
+      </c>
+      <c r="C12">
         <v>28.24703251333219</v>
-      </c>
-      <c r="C12">
-        <v>27.11852743849991</v>
       </c>
       <c r="D12">
         <v>3.540194884287454</v>
       </c>
       <c r="E12">
-        <v>18.18101291051222</v>
+        <v>17.45465819252829</v>
       </c>
       <c r="F12">
         <v>64.36432889695949</v>
       </c>
       <c r="G12">
-        <v>17.45465819252829</v>
+        <v>18.18101291051222</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.34115486635381</v>
+      </c>
+      <c r="C13">
         <v>26.03550295857988</v>
-      </c>
-      <c r="C13">
-        <v>28.34115486635381</v>
       </c>
       <c r="D13">
         <v>3.840909090909091</v>
       </c>
       <c r="E13">
-        <v>16.8649220195612</v>
+        <v>18.35844567803331</v>
       </c>
       <c r="F13">
         <v>64.7766323024055</v>
       </c>
       <c r="G13">
-        <v>18.35844567803331</v>
+        <v>16.8649220195612</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.29259896729776</v>
+      </c>
+      <c r="C14">
         <v>34.20826161790017</v>
-      </c>
-      <c r="C14">
-        <v>30.29259896729776</v>
       </c>
       <c r="D14">
         <v>2.923270440251572</v>
       </c>
       <c r="E14">
-        <v>20.79518702589589</v>
+        <v>18.41485744179964</v>
       </c>
       <c r="F14">
         <v>60.78995553230448</v>
       </c>
       <c r="G14">
-        <v>18.41485744179964</v>
+        <v>20.79518702589589</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>31.51710512633877</v>
+      </c>
+      <c r="C15">
         <v>24.04076115212644</v>
-      </c>
-      <c r="C15">
-        <v>31.51710512633877</v>
       </c>
       <c r="D15">
         <v>4.159602076124568</v>
       </c>
       <c r="E15">
-        <v>15.45454545454546</v>
+        <v>20.26069518716578</v>
       </c>
       <c r="F15">
         <v>64.28475935828877</v>
       </c>
       <c r="G15">
-        <v>20.26069518716578</v>
+        <v>15.45454545454546</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.6804979253112</v>
+      </c>
+      <c r="C16">
         <v>36.47302904564315</v>
-      </c>
-      <c r="C16">
-        <v>26.6804979253112</v>
       </c>
       <c r="D16">
         <v>2.741751990898749</v>
       </c>
       <c r="E16">
-        <v>22.35503560528992</v>
+        <v>16.353001017294</v>
       </c>
       <c r="F16">
         <v>61.29196337741607</v>
       </c>
       <c r="G16">
-        <v>16.353001017294</v>
+        <v>22.35503560528993</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.38496583143508</v>
+      </c>
+      <c r="C17">
         <v>29.58428246013667</v>
-      </c>
-      <c r="C17">
-        <v>29.38496583143508</v>
       </c>
       <c r="D17">
         <v>3.380173243503369</v>
       </c>
       <c r="E17">
-        <v>18.61006627261329</v>
+        <v>18.4846856528748</v>
       </c>
       <c r="F17">
         <v>62.90524807451192</v>
       </c>
       <c r="G17">
-        <v>18.4846856528748</v>
+        <v>18.61006627261329</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>31.63879598662207</v>
+      </c>
+      <c r="C18">
         <v>16.70182660149215</v>
-      </c>
-      <c r="C18">
-        <v>31.63879598662207</v>
       </c>
       <c r="D18">
         <v>5.987369069624153</v>
       </c>
       <c r="E18">
-        <v>11.25910509885536</v>
+        <v>21.32847728061048</v>
       </c>
       <c r="F18">
         <v>67.41241762053417</v>
       </c>
       <c r="G18">
-        <v>21.32847728061048</v>
+        <v>11.25910509885536</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.82375046974822</v>
+      </c>
+      <c r="C19">
         <v>33.16422397594889</v>
-      </c>
-      <c r="C19">
-        <v>28.82375046974822</v>
       </c>
       <c r="D19">
         <v>3.015297450424929</v>
       </c>
       <c r="E19">
-        <v>20.47326296253335</v>
+        <v>17.79375942466071</v>
       </c>
       <c r="F19">
         <v>61.73297761280595</v>
       </c>
       <c r="G19">
-        <v>17.79375942466071</v>
+        <v>20.47326296253335</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>28.3832792517656</v>
+      </c>
+      <c r="C20">
         <v>32.0481007825921</v>
-      </c>
-      <c r="C20">
-        <v>28.3832792517656</v>
       </c>
       <c r="D20">
         <v>3.120309708159619</v>
       </c>
       <c r="E20">
-        <v>19.97620464009519</v>
+        <v>17.6918500892326</v>
       </c>
       <c r="F20">
         <v>62.33194527067222</v>
       </c>
       <c r="G20">
-        <v>17.6918500892326</v>
+        <v>19.97620464009519</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.3591298276559</v>
+      </c>
+      <c r="C21">
         <v>26.35045750192922</v>
-      </c>
-      <c r="C21">
-        <v>29.3591298276559</v>
       </c>
       <c r="D21">
         <v>3.795000522957849</v>
       </c>
       <c r="E21">
+        <v>18.85505596101314</v>
+      </c>
+      <c r="F21">
+        <v>64.22212126754498</v>
+      </c>
+      <c r="G21">
         <v>16.92282277144189</v>
-      </c>
-      <c r="F21">
-        <v>64.22212126754496</v>
-      </c>
-      <c r="G21">
-        <v>18.85505596101314</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>31.4409690833484</v>
+      </c>
+      <c r="C22">
         <v>30.59121316217682</v>
-      </c>
-      <c r="C22">
-        <v>31.4409690833484</v>
       </c>
       <c r="D22">
         <v>3.268912529550827</v>
       </c>
       <c r="E22">
-        <v>18.87971434947557</v>
+        <v>19.40415085918322</v>
       </c>
       <c r="F22">
         <v>61.71613479134123</v>
       </c>
       <c r="G22">
-        <v>19.40415085918322</v>
+        <v>18.87971434947557</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>29.40816170277927</v>
+      </c>
+      <c r="C23">
         <v>33.98667789602634</v>
-      </c>
-      <c r="C23">
-        <v>29.40816170277927</v>
       </c>
       <c r="D23">
         <v>2.942329353457986</v>
       </c>
       <c r="E23">
-        <v>20.80033737875451</v>
+        <v>17.99821938990675</v>
       </c>
       <c r="F23">
         <v>61.20144323133874</v>
       </c>
       <c r="G23">
-        <v>17.99821938990675</v>
+        <v>20.80033737875451</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>25.4577376473539</v>
+      </c>
+      <c r="C24">
         <v>30.76247805367444</v>
-      </c>
-      <c r="C24">
-        <v>25.4577376473539</v>
       </c>
       <c r="D24">
         <v>3.25071341214839</v>
       </c>
       <c r="E24">
-        <v>19.69173958416954</v>
+        <v>16.29605844103717</v>
       </c>
       <c r="F24">
         <v>64.01220197479329</v>
       </c>
       <c r="G24">
-        <v>16.29605844103717</v>
+        <v>19.69173958416954</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.65118157947889</v>
+      </c>
+      <c r="C25">
         <v>33.58917390426176</v>
-      </c>
-      <c r="C25">
-        <v>26.65118157947889</v>
       </c>
       <c r="D25">
         <v>2.97714972940469</v>
       </c>
       <c r="E25">
-        <v>20.96174450116594</v>
+        <v>16.63200352933762</v>
       </c>
       <c r="F25">
         <v>62.40625196949643</v>
       </c>
       <c r="G25">
-        <v>16.63200352933762</v>
+        <v>20.96174450116594</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.13590084108012</v>
+      </c>
+      <c r="C26">
         <v>42.56308100929615</v>
-      </c>
-      <c r="C26">
-        <v>27.13590084108012</v>
       </c>
       <c r="D26">
         <v>2.349453978159126</v>
       </c>
       <c r="E26">
-        <v>25.08151819486109</v>
+        <v>15.990609103952</v>
       </c>
       <c r="F26">
         <v>58.92787270118691</v>
       </c>
       <c r="G26">
-        <v>15.990609103952</v>
+        <v>25.08151819486109</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>22.79039584685269</v>
+      </c>
+      <c r="C27">
         <v>34.63984425697599</v>
-      </c>
-      <c r="C27">
-        <v>22.79039584685269</v>
       </c>
       <c r="D27">
         <v>2.886849007118771</v>
       </c>
       <c r="E27">
-        <v>22.0032976092333</v>
+        <v>14.4765045342127</v>
       </c>
       <c r="F27">
-        <v>63.52019785655398</v>
+        <v>63.520197856554</v>
       </c>
       <c r="G27">
-        <v>14.47650453421269</v>
+        <v>22.00329760923331</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>26.60401814646792</v>
+      </c>
+      <c r="C28">
         <v>27.0252754374595</v>
-      </c>
-      <c r="C28">
-        <v>26.60401814646792</v>
       </c>
       <c r="D28">
         <v>3.700239808153477</v>
       </c>
       <c r="E28">
-        <v>17.59122547985657</v>
+        <v>17.31702172537439</v>
       </c>
       <c r="F28">
         <v>65.09175279476904</v>
       </c>
       <c r="G28">
-        <v>17.31702172537439</v>
+        <v>17.59122547985657</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>39.01569186875891</v>
+      </c>
+      <c r="C29">
         <v>33.45221112696149</v>
-      </c>
-      <c r="C29">
-        <v>39.01569186875891</v>
       </c>
       <c r="D29">
         <v>2.989339019189766</v>
       </c>
       <c r="E29">
-        <v>19.39619520264682</v>
+        <v>22.62200165425972</v>
       </c>
       <c r="F29">
         <v>57.98180314309347</v>
       </c>
       <c r="G29">
-        <v>22.62200165425972</v>
+        <v>19.39619520264682</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>32.56634195498825</v>
+      </c>
+      <c r="C30">
         <v>24.33658045011757</v>
-      </c>
-      <c r="C30">
-        <v>32.56634195498825</v>
       </c>
       <c r="D30">
         <v>4.10904071773637</v>
       </c>
       <c r="E30">
-        <v>15.51059730250482</v>
+        <v>20.75572682509099</v>
       </c>
       <c r="F30">
         <v>63.7336758724042</v>
       </c>
       <c r="G30">
-        <v>20.75572682509099</v>
+        <v>15.51059730250482</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>30.97913322632424</v>
+      </c>
+      <c r="C31">
         <v>34.99197431781702</v>
-      </c>
-      <c r="C31">
-        <v>30.97913322632424</v>
       </c>
       <c r="D31">
         <v>2.857798165137615</v>
       </c>
       <c r="E31">
-        <v>21.08317214700194</v>
+        <v>18.66537717601547</v>
       </c>
       <c r="F31">
         <v>60.25145067698259</v>
       </c>
       <c r="G31">
-        <v>18.66537717601547</v>
+        <v>21.08317214700194</v>
       </c>
     </row>
   </sheetData>
